--- a/design_issues/codescene/P1_CVBuilder.xlsx
+++ b/design_issues/codescene/P1_CVBuilder.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI IDE Analysis\AI-IDEs-code-analysis\design_issues\codescene\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DIinAGP\DIinAGP\design_issues\codescene\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="152">
   <si>
     <t>resource</t>
   </si>
@@ -232,12 +232,6 @@
     <t>Primitive Obsession ()</t>
   </si>
   <si>
-    <t>String Heavy Function Arguments</t>
-  </si>
-  <si>
-    <t>String Heavy Function Arguments ()</t>
-  </si>
-  <si>
     <t>Large Method (LoC = 129 lines)</t>
   </si>
   <si>
@@ -437,9 +431,6 @@
   </si>
   <si>
     <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/P1_CVBuilder/frontend/src/services/authService.ts</t>
-  </si>
-  <si>
-    <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/P1_CVBuilder/frontend/src/services/awardService.ts</t>
   </si>
   <si>
     <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/P1_CVBuilder/frontend/src/services/cvService.ts</t>
@@ -882,11 +873,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E227"/>
+  <dimension ref="A1:E218"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="100.26953125" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" customWidth="1"/>
     <col min="3" max="3" width="48.90625" customWidth="1"/>
     <col min="4" max="4" width="23.36328125" customWidth="1"/>
     <col min="5" max="5" width="36.36328125" customWidth="1"/>
@@ -911,7 +902,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -928,7 +919,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -945,7 +936,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -962,7 +953,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -979,7 +970,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -996,7 +987,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1013,7 +1004,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -1030,7 +1021,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
@@ -1047,7 +1038,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
@@ -1064,7 +1055,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
@@ -1081,7 +1072,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
@@ -1098,7 +1089,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
@@ -1115,7 +1106,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
@@ -1132,7 +1123,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
@@ -1149,7 +1140,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
@@ -1166,7 +1157,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
@@ -1183,7 +1174,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
@@ -1200,7 +1191,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
@@ -1217,7 +1208,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -1234,7 +1225,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
@@ -1251,7 +1242,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
@@ -1268,7 +1259,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
@@ -1285,7 +1276,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
@@ -1302,7 +1293,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
@@ -1319,7 +1310,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
@@ -1336,7 +1327,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
@@ -1353,7 +1344,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
         <v>18</v>
@@ -1370,7 +1361,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -1387,7 +1378,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
@@ -1404,7 +1395,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -1421,7 +1412,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -1438,7 +1429,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
@@ -1455,7 +1446,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
@@ -1472,7 +1463,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
@@ -1489,7 +1480,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
@@ -1506,7 +1497,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
         <v>5</v>
@@ -1523,7 +1514,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -1540,7 +1531,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -1557,7 +1548,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
@@ -1574,7 +1565,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -1591,7 +1582,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
@@ -1608,7 +1599,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
         <v>5</v>
@@ -1625,7 +1616,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
@@ -1642,7 +1633,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
@@ -1659,7 +1650,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
@@ -1676,7 +1667,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
@@ -1693,7 +1684,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
@@ -1710,7 +1701,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -1727,7 +1718,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B50" t="s">
         <v>5</v>
@@ -1744,7 +1735,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
         <v>5</v>
@@ -1761,7 +1752,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B52" t="s">
         <v>5</v>
@@ -1778,7 +1769,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
         <v>5</v>
@@ -1795,7 +1786,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B54" t="s">
         <v>5</v>
@@ -1812,7 +1803,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B55" t="s">
         <v>5</v>
@@ -1829,7 +1820,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
@@ -1846,7 +1837,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B57" t="s">
         <v>5</v>
@@ -1863,7 +1854,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B58" t="s">
         <v>5</v>
@@ -1880,7 +1871,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B59" t="s">
         <v>5</v>
@@ -1897,7 +1888,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B60" t="s">
         <v>5</v>
@@ -1914,7 +1905,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B61" t="s">
         <v>29</v>
@@ -1931,7 +1922,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
@@ -1948,7 +1939,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
@@ -1965,7 +1956,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -1982,7 +1973,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
@@ -1999,7 +1990,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
@@ -2016,7 +2007,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B67" t="s">
         <v>9</v>
@@ -2033,7 +2024,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B68" t="s">
         <v>9</v>
@@ -2050,7 +2041,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
         <v>34</v>
@@ -2067,7 +2058,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
         <v>9</v>
@@ -2084,7 +2075,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -2101,7 +2092,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B72" t="s">
         <v>9</v>
@@ -2118,7 +2109,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
@@ -2135,7 +2126,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
@@ -2152,7 +2143,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B75" t="s">
         <v>9</v>
@@ -2169,7 +2160,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -2186,7 +2177,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -2203,7 +2194,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B78" t="s">
         <v>9</v>
@@ -2220,7 +2211,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -2237,7 +2228,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B80" t="s">
         <v>9</v>
@@ -2254,7 +2245,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
@@ -2271,7 +2262,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B82" t="s">
         <v>9</v>
@@ -2288,7 +2279,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
@@ -2305,7 +2296,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B84" t="s">
         <v>9</v>
@@ -2322,7 +2313,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B85" t="s">
         <v>11</v>
@@ -2339,7 +2330,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B86" t="s">
         <v>9</v>
@@ -2356,7 +2347,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B87" t="s">
         <v>11</v>
@@ -2373,7 +2364,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B88" t="s">
         <v>9</v>
@@ -2390,7 +2381,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B89" t="s">
         <v>11</v>
@@ -2407,7 +2398,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B90" t="s">
         <v>9</v>
@@ -2424,7 +2415,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B91" t="s">
         <v>11</v>
@@ -2441,7 +2432,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B92" t="s">
         <v>9</v>
@@ -2458,7 +2449,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B93" t="s">
         <v>9</v>
@@ -2475,7 +2466,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B94" t="s">
         <v>9</v>
@@ -2492,7 +2483,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -2509,7 +2500,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B96" t="s">
         <v>9</v>
@@ -2526,7 +2517,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -2543,7 +2534,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B98" t="s">
         <v>9</v>
@@ -2560,7 +2551,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B99" t="s">
         <v>11</v>
@@ -2577,7 +2568,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B100" t="s">
         <v>7</v>
@@ -2594,7 +2585,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B101" t="s">
         <v>9</v>
@@ -2611,7 +2602,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B102" t="s">
         <v>13</v>
@@ -2628,7 +2619,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B103" t="s">
         <v>9</v>
@@ -2645,7 +2636,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B104" t="s">
         <v>11</v>
@@ -2662,7 +2653,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B105" t="s">
         <v>9</v>
@@ -2679,7 +2670,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B106" t="s">
         <v>9</v>
@@ -2696,7 +2687,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B107" t="s">
         <v>9</v>
@@ -2713,7 +2704,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
@@ -2730,7 +2721,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B109" t="s">
         <v>9</v>
@@ -2747,7 +2738,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B110" t="s">
         <v>11</v>
@@ -2764,7 +2755,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
@@ -2781,7 +2772,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B112" t="s">
         <v>9</v>
@@ -2798,7 +2789,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
@@ -2815,7 +2806,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B114" t="s">
         <v>13</v>
@@ -2832,7 +2823,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B115" t="s">
         <v>13</v>
@@ -2849,7 +2840,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
@@ -2866,7 +2857,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B117" t="s">
         <v>9</v>
@@ -2883,7 +2874,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B118" t="s">
         <v>11</v>
@@ -2900,7 +2891,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B119" t="s">
         <v>9</v>
@@ -2917,7 +2908,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B120" t="s">
         <v>11</v>
@@ -2934,7 +2925,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B121" t="s">
         <v>5</v>
@@ -2951,7 +2942,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B122" t="s">
         <v>5</v>
@@ -2968,7 +2959,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B123" t="s">
         <v>9</v>
@@ -2985,7 +2976,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B124" t="s">
         <v>11</v>
@@ -3002,7 +2993,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B125" t="s">
         <v>9</v>
@@ -3019,7 +3010,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B126" t="s">
         <v>9</v>
@@ -3036,7 +3027,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B127" t="s">
         <v>11</v>
@@ -3053,7 +3044,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B128" t="s">
         <v>9</v>
@@ -3070,7 +3061,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B129" t="s">
         <v>9</v>
@@ -3087,7 +3078,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B130" t="s">
         <v>11</v>
@@ -3104,7 +3095,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B131" t="s">
         <v>9</v>
@@ -3121,7 +3112,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B132" t="s">
         <v>9</v>
@@ -3138,7 +3129,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B133" t="s">
         <v>11</v>
@@ -3155,7 +3146,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
@@ -3172,7 +3163,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B135" t="s">
         <v>5</v>
@@ -3189,7 +3180,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B136" t="s">
         <v>5</v>
@@ -3206,7 +3197,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B137" t="s">
         <v>5</v>
@@ -3223,7 +3214,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B138" t="s">
         <v>5</v>
@@ -3240,7 +3231,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B139" t="s">
         <v>7</v>
@@ -3257,7 +3248,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B140" t="s">
         <v>9</v>
@@ -3274,7 +3265,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B141" t="s">
         <v>5</v>
@@ -3291,7 +3282,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B142" t="s">
         <v>5</v>
@@ -3308,7 +3299,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B143" t="s">
         <v>5</v>
@@ -3325,7 +3316,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B144" t="s">
         <v>7</v>
@@ -3342,7 +3333,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B145" t="s">
         <v>9</v>
@@ -3359,7 +3350,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B146" t="s">
         <v>5</v>
@@ -3376,7 +3367,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B147" t="s">
         <v>5</v>
@@ -3393,7 +3384,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B148" t="s">
         <v>5</v>
@@ -3410,7 +3401,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B149" t="s">
         <v>5</v>
@@ -3427,7 +3418,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B150" t="s">
         <v>5</v>
@@ -3444,7 +3435,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B151" t="s">
         <v>5</v>
@@ -3461,7 +3452,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B152" t="s">
         <v>5</v>
@@ -3478,7 +3469,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B153" t="s">
         <v>9</v>
@@ -3495,7 +3486,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B154" t="s">
         <v>11</v>
@@ -3512,7 +3503,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B155" t="s">
         <v>9</v>
@@ -3529,7 +3520,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B156" t="s">
         <v>11</v>
@@ -3546,7 +3537,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B157" t="s">
         <v>9</v>
@@ -3563,7 +3554,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B158" t="s">
         <v>9</v>
@@ -3580,7 +3571,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B159" t="s">
         <v>11</v>
@@ -3597,7 +3588,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B160" t="s">
         <v>9</v>
@@ -3614,7 +3605,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B161" t="s">
         <v>11</v>
@@ -3631,7 +3622,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B162" t="s">
         <v>9</v>
@@ -3648,7 +3639,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B163" t="s">
         <v>9</v>
@@ -3665,7 +3656,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B164" t="s">
         <v>11</v>
@@ -3682,7 +3673,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B165" t="s">
         <v>68</v>
@@ -3699,115 +3690,115 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" t="s">
         <v>70</v>
       </c>
-      <c r="C166" t="s">
-        <v>71</v>
-      </c>
       <c r="D166">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B167" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C167" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D167">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E167">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B168" t="s">
         <v>9</v>
       </c>
       <c r="C168" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D168">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="E168">
-        <v>8</v>
+        <v>98</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B169" t="s">
         <v>9</v>
       </c>
       <c r="C169" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D169">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="E169">
-        <v>98</v>
+        <v>130</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B170" t="s">
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D170">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="E170">
-        <v>130</v>
+        <v>39</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B171" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C171" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D171">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E171">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B172" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="C172" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -3818,13 +3809,13 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B173" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C173" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -3835,262 +3826,262 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B174" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C174" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="E174">
-        <v>1</v>
+        <v>199</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B175" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C175" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="D175">
-        <v>1</v>
+        <v>202</v>
       </c>
       <c r="E175">
-        <v>1</v>
+        <v>202</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B176" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C176" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>206</v>
       </c>
       <c r="E176">
-        <v>1</v>
+        <v>206</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B177" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C177" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="D177">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="E177">
-        <v>1</v>
+        <v>210</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B178" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="D178">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="E178">
-        <v>199</v>
+        <v>218</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B179" t="s">
         <v>13</v>
       </c>
       <c r="C179" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D179">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="E179">
-        <v>202</v>
+        <v>222</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B180" t="s">
         <v>13</v>
       </c>
       <c r="C180" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D180">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="E180">
-        <v>206</v>
+        <v>226</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B181" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C181" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="D181">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="E181">
-        <v>210</v>
+        <v>170</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B182" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C182" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D182">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="E182">
-        <v>218</v>
+        <v>170</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B183" t="s">
         <v>13</v>
       </c>
       <c r="C183" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D183">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="E183">
-        <v>222</v>
+        <v>173</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B184" t="s">
         <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D184">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="E184">
-        <v>226</v>
+        <v>177</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B185" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D185">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="E185">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B186" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C186" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="D186">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="E186">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B187" t="s">
         <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D187">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="E187">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B188" t="s">
         <v>13</v>
       </c>
       <c r="C188" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D188">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E188">
-        <v>177</v>
+        <v>199</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B189" t="s">
         <v>13</v>
@@ -4099,61 +4090,61 @@
         <v>14</v>
       </c>
       <c r="D189">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="E189">
-        <v>185</v>
+        <v>203</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B190" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C190" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D190">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="E190">
-        <v>189</v>
+        <v>71</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B191" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C191" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D191">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="E191">
-        <v>195</v>
+        <v>83</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B192" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C192" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D192">
-        <v>199</v>
+        <v>1</v>
       </c>
       <c r="E192">
-        <v>199</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
@@ -4161,21 +4152,21 @@
         <v>142</v>
       </c>
       <c r="B193" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C193" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D193">
-        <v>203</v>
+        <v>102</v>
       </c>
       <c r="E193">
-        <v>203</v>
+        <v>102</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B194" t="s">
         <v>5</v>
@@ -4184,15 +4175,15 @@
         <v>6</v>
       </c>
       <c r="D194">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E194">
-        <v>71</v>
+        <v>114</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B195" t="s">
         <v>5</v>
@@ -4201,38 +4192,38 @@
         <v>6</v>
       </c>
       <c r="D195">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="E195">
-        <v>83</v>
+        <v>137</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B196" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C196" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="D196">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="E196">
-        <v>1</v>
+        <v>149</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B197" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C197" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -4243,98 +4234,98 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B198" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="C198" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D198">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c r="E198">
-        <v>1</v>
+        <v>310</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B199" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C199" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="D199">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="E199">
-        <v>102</v>
+        <v>310</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B200" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C200" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D200">
-        <v>114</v>
+        <v>313</v>
       </c>
       <c r="E200">
-        <v>114</v>
+        <v>313</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B201" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C201" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D201">
-        <v>137</v>
+        <v>317</v>
       </c>
       <c r="E201">
-        <v>137</v>
+        <v>317</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B202" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C202" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D202">
-        <v>149</v>
+        <v>335</v>
       </c>
       <c r="E202">
-        <v>149</v>
+        <v>335</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B203" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="C203" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -4345,13 +4336,13 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B204" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C204" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -4362,392 +4353,239 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B205" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C205" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="D205">
-        <v>310</v>
+        <v>1</v>
       </c>
       <c r="E205">
-        <v>310</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B206" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C206" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D206">
-        <v>310</v>
+        <v>27</v>
       </c>
       <c r="E206">
-        <v>310</v>
+        <v>27</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B207" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C207" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D207">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="E207">
-        <v>313</v>
+        <v>291</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B208" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C208" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D208">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="E208">
-        <v>317</v>
+        <v>291</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B209" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C209" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D209">
-        <v>335</v>
+        <v>560</v>
       </c>
       <c r="E209">
-        <v>335</v>
+        <v>560</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B210" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C210" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>903</v>
       </c>
       <c r="E210">
-        <v>1</v>
+        <v>903</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B211" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C211" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D211">
-        <v>1</v>
+        <v>1213</v>
       </c>
       <c r="E211">
-        <v>1</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B212" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>1213</v>
       </c>
       <c r="E212">
-        <v>1</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B213" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C213" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D213">
-        <v>27</v>
+        <v>1503</v>
       </c>
       <c r="E213">
-        <v>27</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B214" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C214" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="D214">
-        <v>291</v>
+        <v>1503</v>
       </c>
       <c r="E214">
-        <v>291</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B215" t="s">
         <v>11</v>
       </c>
       <c r="C215" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D215">
-        <v>291</v>
+        <v>1713</v>
       </c>
       <c r="E215">
-        <v>291</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B216" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C216" t="s">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="D216">
-        <v>560</v>
+        <v>155</v>
       </c>
       <c r="E216">
-        <v>560</v>
+        <v>155</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B217" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C217" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="D217">
-        <v>903</v>
+        <v>177</v>
       </c>
       <c r="E217">
-        <v>903</v>
+        <v>177</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B218" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C218" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="D218">
-        <v>1213</v>
+        <v>1</v>
       </c>
       <c r="E218">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A219" t="s">
-        <v>148</v>
-      </c>
-      <c r="B219" t="s">
-        <v>11</v>
-      </c>
-      <c r="C219" t="s">
-        <v>80</v>
-      </c>
-      <c r="D219">
-        <v>1213</v>
-      </c>
-      <c r="E219">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
-        <v>148</v>
-      </c>
-      <c r="B220" t="s">
-        <v>9</v>
-      </c>
-      <c r="C220" t="s">
-        <v>58</v>
-      </c>
-      <c r="D220">
-        <v>1503</v>
-      </c>
-      <c r="E220">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A221" t="s">
-        <v>148</v>
-      </c>
-      <c r="B221" t="s">
-        <v>11</v>
-      </c>
-      <c r="C221" t="s">
-        <v>81</v>
-      </c>
-      <c r="D221">
-        <v>1503</v>
-      </c>
-      <c r="E221">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
-        <v>148</v>
-      </c>
-      <c r="B222" t="s">
-        <v>11</v>
-      </c>
-      <c r="C222" t="s">
-        <v>82</v>
-      </c>
-      <c r="D222">
-        <v>1713</v>
-      </c>
-      <c r="E222">
-        <v>1713</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A223" t="s">
-        <v>149</v>
-      </c>
-      <c r="B223" t="s">
-        <v>70</v>
-      </c>
-      <c r="C223" t="s">
-        <v>71</v>
-      </c>
-      <c r="D223">
-        <v>1</v>
-      </c>
-      <c r="E223">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
-        <v>149</v>
-      </c>
-      <c r="B224" t="s">
-        <v>5</v>
-      </c>
-      <c r="C224" t="s">
-        <v>6</v>
-      </c>
-      <c r="D224">
-        <v>155</v>
-      </c>
-      <c r="E224">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A225" t="s">
-        <v>149</v>
-      </c>
-      <c r="B225" t="s">
-        <v>5</v>
-      </c>
-      <c r="C225" t="s">
-        <v>6</v>
-      </c>
-      <c r="D225">
-        <v>177</v>
-      </c>
-      <c r="E225">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A226" t="s">
-        <v>150</v>
-      </c>
-      <c r="B226" t="s">
-        <v>68</v>
-      </c>
-      <c r="C226" t="s">
-        <v>69</v>
-      </c>
-      <c r="D226">
-        <v>1</v>
-      </c>
-      <c r="E226">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
-        <v>150</v>
-      </c>
-      <c r="B227" t="s">
-        <v>70</v>
-      </c>
-      <c r="C227" t="s">
-        <v>71</v>
-      </c>
-      <c r="D227">
-        <v>1</v>
-      </c>
-      <c r="E227">
         <v>1</v>
       </c>
     </row>
@@ -4758,7 +4596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:C15"/>
+  <dimension ref="A3:C14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="44.1796875" customWidth="1"/>
@@ -4767,13 +4605,13 @@
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -4784,7 +4622,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIF(Issues!B2:B227,B4)</f>
+        <f>COUNTIF(Issues!B2:B218,B4)</f>
         <v>64</v>
       </c>
     </row>
@@ -4796,7 +4634,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(Issues!B2:B228,B5)</f>
+        <f>COUNTIF(Issues!B2:B219,B5)</f>
         <v>10</v>
       </c>
     </row>
@@ -4808,7 +4646,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIF(Issues!B2:B229,B6)</f>
+        <f>COUNTIF(Issues!B2:B220,B6)</f>
         <v>62</v>
       </c>
     </row>
@@ -4820,7 +4658,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIF(Issues!B2:B230,B7)</f>
+        <f>COUNTIF(Issues!B2:B221,B7)</f>
         <v>37</v>
       </c>
     </row>
@@ -4832,7 +4670,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIF(Issues!B2:B231,B8)</f>
+        <f>COUNTIF(Issues!B2:B222,B8)</f>
         <v>30</v>
       </c>
     </row>
@@ -4844,7 +4682,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIF(Issues!B2:B232,B9)</f>
+        <f>COUNTIF(Issues!B2:B223,B9)</f>
         <v>2</v>
       </c>
     </row>
@@ -4856,7 +4694,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="3">
-        <f>COUNTIF(Issues!B2:B233,B10)</f>
+        <f>COUNTIF(Issues!B2:B224,B10)</f>
         <v>2</v>
       </c>
     </row>
@@ -4868,7 +4706,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="3">
-        <f>COUNTIF(Issues!B2:B234,B11)</f>
+        <f>COUNTIF(Issues!B2:B225,B11)</f>
         <v>1</v>
       </c>
     </row>
@@ -4880,7 +4718,7 @@
         <v>34</v>
       </c>
       <c r="C12" s="3">
-        <f>COUNTIF(Issues!B2:B235,B12)</f>
+        <f>COUNTIF(Issues!B2:B226,B12)</f>
         <v>3</v>
       </c>
     </row>
@@ -4892,30 +4730,18 @@
         <v>68</v>
       </c>
       <c r="C13" s="3">
-        <f>COUNTIF(Issues!B2:B236,B13)</f>
+        <f>COUNTIF(Issues!B2:B227,B13)</f>
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>11</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="3">
-        <f>COUNTIF(Issues!B2:B237,B14)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="4"/>
-      <c r="B15" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="5">
-        <f>SUM(C4:C14)</f>
-        <v>226</v>
+      <c r="A14" s="4"/>
+      <c r="B14" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="5">
+        <f>SUM(C4:C13)</f>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
